--- a/pdf/01_撮影機材と費用.xlsx
+++ b/pdf/01_撮影機材と費用.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0;(#,##0);-"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -77,6 +77,12 @@
       <b val="1"/>
       <color rgb="001A1A1A"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <name val="Meiryo"/>
+      <b val="1"/>
+      <color rgb="001A1A1A"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Meiryo"/>
@@ -145,7 +151,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -175,21 +181,25 @@
     <xf numFmtId="3" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -555,15 +565,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="52" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -583,7 +594,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>動画8本を1人で撮影する前提。機材は現在なにも所有していないため、ゼロから揃える場合の金額です。</t>
+          <t>動画8本を1人で撮影する前提。カメラはお手持ちのものを使用し、それ以外に必要な機材の金額です。</t>
         </is>
       </c>
     </row>
@@ -632,529 +643,562 @@
           <t>商品ページ</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="42" customHeight="1">
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>リンクの確認結果</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="48" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>カメラ本体</t>
+          <t>マクロレンズ</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>SONY ZV-E10 標準ズームレンズキット</t>
+          <t>SONY E 30mm F3.5 Macro（SEL30M35）</t>
         </is>
       </c>
       <c r="C9" s="8" t="n">
-        <v>82800</v>
+        <v>27800</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>8本すべての撮影本体。瞳AF・4K・外部マイク端子つき。動画向けの現行機では実売最安クラス</t>
+          <t>刃が革に入る瞬間・コバ塗り・刻印の寄り。②③⑤の核になるカットはこのレンズがないと撮れない</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>ソニー公式・国内正規品</t>
+          <t>ソニー純正・等倍マクロ</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B09BC33J91</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="42" customHeight="1">
+          <t>https://www.amazon.co.jp/dp/B0055MFTHM</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>確認済（ソニー 単焦点レンズ APS-C専用 SEL30M35）※ソニーEマウント専用。お使いのカメラのマウント要確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>スマホ</t>
+          <t>三脚（雲台付き）</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>手持ちのものを使用</t>
+          <t>Velbon EX-440</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>0</v>
+        <v>3012</v>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>2台目のカメラとして別アングルの押さえ、作業音の別録りに使用</t>
+          <t>③⑦の固定撮影と、①⑤⑥の真俯瞰。1人で撮るのでカメラを置ける三脚は必須</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>購入不要</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr"/>
-    </row>
-    <row r="11" ht="42" customHeight="1">
+          <t>国内カメラ用品の老舗メーカー・入門定番</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.jp/dp/B0053CEPQU</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>確認済（Velbon ファミリー三脚 EX-440 4段 全高153cm 3Way雲台付）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="48" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>マクロレンズ</t>
+          <t>音声レコーダー</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>SONY E 30mm F3.5 Macro（SEL30M35）</t>
+          <t>ZOOM H1essential</t>
         </is>
       </c>
       <c r="C11" s="8" t="n">
-        <v>27800</v>
+        <v>12626</v>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>刃が革に入る瞬間・コバ塗り・刻印の寄り。②③⑤の核になるカットはこのレンズがないと撮れない</t>
+          <t>永尾社長・佐藤さん・くさがやさん・購入者の4人分のインタビュー音声。⑤は社長の声だけで全編が進むため最重要</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>ソニー純正・等倍マクロ</t>
+          <t>ZOOM公式・評価4.5／5（32件）・32bitフロートで音割れしない</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0055MFTHM</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="42" customHeight="1">
+          <t>https://www.amazon.co.jp/dp/B0CSL4PXDV</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>確認済（ZOOM 32bitフロートハンディレコーダー H1essential）※前回の検索リンクから商品ページに修正</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="48" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>三脚（雲台付き）</t>
+          <t>ガンマイク</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Velbon EX-440</t>
+          <t>RODE VideoMic GO II</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>3012</v>
+        <v>16364</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>③⑦の固定撮影と、①⑤⑥の真俯瞰。1人で撮るのでカメラを置ける三脚は必須</t>
+          <t>カメラに載せる指向性マイク。工房の環境音の中から刃の音・ミシンの音・コバを磨く音だけを拾う。電池不要</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>国内カメラ用品の老舗メーカー・入門定番</t>
+          <t>RODE公式・入門ガンマイクの定番機</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0053CEPQU</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="42" customHeight="1">
+          <t>https://www.amazon.co.jp/dp/B09MRLGL7G</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>修正（前回は米国Amazon由来のASINでした。実売16,364円の出どころもこの国内ページです）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="48" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>音声レコーダー</t>
+          <t>照明（LED1灯）</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>ZOOM H1essential</t>
+          <t>Neewer 二色660 LEDビデオライト</t>
         </is>
       </c>
       <c r="C13" s="8" t="n">
-        <v>12626</v>
+        <v>10949</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>永尾社長・佐藤さん・くさがやさん・購入者の4人分のインタビュー音声。⑤は社長の声だけで全編が進むため最重要</t>
+          <t>③「黒い布一枚とライト一灯」の要。工房の蛍光灯を全部消して撮るので、この1灯が画をつくる</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>ZOOM公式・評価4.5／5（32件）・32bitフロートで音割れしない</t>
+          <t>Neewer公式・レビュー多数の定番モデル</t>
         </is>
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/s?k=ZOOM+H1essential</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="42" customHeight="1">
+          <t>https://www.amazon.co.jp/dp/B077Z61TPN</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>確認済（Neewer 調光可能な二色660 LEDビデオライト・CRI96+）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="48" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>ガンマイク</t>
+          <t>レフ板</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>RODE VideoMic GO II</t>
+          <t>EMART レフ板 60cm 丸レフ板 5in1</t>
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>16364</v>
+        <v>1099</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>カメラに載せる指向性マイク。工房の環境音の中から刃の音・ミシンの音・コバを磨く音だけを拾う。電池不要</t>
+          <t>1灯だけだと影が硬くなるので反対側から起こす。屋外（①④）でも手元に光を回せる</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>RODE公式・入門ガンマイクの定番機</t>
+          <t>レビュー件数の多い定番品</t>
         </is>
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0D3QSNXW9</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="42" customHeight="1">
+          <t>https://www.amazon.co.jp/dp/B0CHNY19K3</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>確認済（EMART レフ板 60cm撮影用 丸レフ板 5in1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="48" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>照明（LED1灯）</t>
+          <t>黒スチレンボード</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Neewer 二色660 LEDビデオライト</t>
+          <t>ブラックスチレンボード A2・5mm厚 ×2枚</t>
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>10949</v>
+        <v>1122</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>③「黒い布一枚とライト一灯」の要。工房の蛍光灯を全部消して撮るので、この1灯が画をつくる</t>
+          <t>③の黒背景と、余計な光を止める遮光板。布より角が立つので黒の中に製品だけを浮かせられる</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>Neewer公式・レビュー多数の定番モデル</t>
+          <t>看板・POP資材の定番（1枚561円）</t>
         </is>
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B077Z61TPN</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="42" customHeight="1">
+          <t>https://www.signmall.jp/item/10899910261.html</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>確認済（サインモール ブラックスチレンボード 5mm厚 A2・561円）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="48" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>レフ板</t>
+          <t>アクリル板</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>5in1レフ板／ディフューザー 60cm</t>
+          <t>PULUZ アクリル反射板 40cm（黒）</t>
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>1099</v>
+        <v>3000</v>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>1灯だけだと影が硬くなるので反対側から起こす。屋外（①④）でも手元に光を回せる</t>
+          <t>製品を映り込ませる台。③の完成品カットと⑦の白台に、鏡面のリフレクションが1枚入る</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>レビュー件数の多い定番品</t>
+          <t>PULUZ公式ショップ</t>
         </is>
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0CHNY19K3</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="42" customHeight="1">
+          <t>https://www.amazon.co.jp/dp/B0C49DT18X</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>確認済（PULUZ アクリル反射板 40cm 黒）※価格は購入時に要確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="48" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>黒スチレンボード</t>
+          <t>SDカード（任意）</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>ブラックスチレンボード A2・5mm厚 ×2枚</t>
+          <t>SanDisk Extreme 128GB（V30以上）</t>
         </is>
       </c>
       <c r="C17" s="8" t="n">
-        <v>1122</v>
+        <v>2500</v>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>③の黒背景と、余計な光を止める遮光板。布より角が立つので黒の中に製品だけを浮かせられる</t>
+          <t>お使いのカメラのカードをそのまま使えるなら不要。4K動画を撮るので書き込み速度はV30以上のもの</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>看板・POP資材の定番（1枚561円）</t>
+          <t>型番はカメラのカード形式（SD／microSD）に合わせて選ぶ</t>
         </is>
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>https://www.signmall.jp/item/10899910261.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="42" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>アクリル板</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>PULUZ アクリル反射板 40cm（黒）</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="n">
-        <v>3000</v>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>製品を映り込ませる台。③の完成品カットと⑦の白台に、鏡面のリフレクションが1枚入る</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>PULUZ公式ショップ／価格は購入時に要確認</t>
-        </is>
-      </c>
-      <c r="F18" s="9" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/dp/B0C49DT18X</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="42" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>SDカード</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>SanDisk Extreme 128GB（V30）</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="n">
-        <v>2500</v>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>カメラに1枚も入っていないと撮影自体ができない。4K動画なので書き込み速度はV30以上</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>サンディスク正規品／価格は購入時に要確認</t>
-        </is>
-      </c>
-      <c r="F19" s="9" t="inlineStr">
-        <is>
           <t>https://www.amazon.co.jp/s?k=SanDisk+Extreme+SD+128GB+V30</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>商品ページ未特定のため検索リンク。カメラに合う形式を確認してから購入</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B20" s="11" t="n"/>
-      <c r="C20" s="12">
-        <f>SUM(C9:C19)</f>
+      <c r="B18" s="11" t="n"/>
+      <c r="C18" s="12">
+        <f>SUM(C9:C17)</f>
         <v/>
       </c>
-      <c r="D20" s="13" t="inlineStr">
+      <c r="D18" s="13" t="inlineStr">
         <is>
           <t>アクリル板とSDカードは概算です。発注時に確定します。</t>
         </is>
       </c>
-      <c r="E20" s="11" t="n"/>
-      <c r="F20" s="11" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>うちカメラ本体</t>
-        </is>
-      </c>
-      <c r="C23" s="14">
-        <f>C9</f>
+      <c r="E18" s="11" t="n"/>
+      <c r="F18" s="11" t="n"/>
+      <c r="G18" s="11" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>うちSDカード（任意）</t>
+        </is>
+      </c>
+      <c r="C21" s="14">
+        <f>C17</f>
         <v/>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>カメラを除いた小計</t>
-        </is>
-      </c>
-      <c r="C24" s="14">
-        <f>C20-C9</f>
+    <row r="22">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>SDカードを買わない場合</t>
+        </is>
+      </c>
+      <c r="C22" s="16">
+        <f>C18-C17</f>
         <v/>
       </c>
-      <c r="D24" s="1" t="inlineStr">
-        <is>
-          <t>カメラを社内から借りられる場合はこの金額</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="15" t="inlineStr">
+      <c r="D22" s="1" t="inlineStr">
+        <is>
+          <t>お使いのカメラのSDカードをそのまま使える場合はこの金額</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="17" t="inlineStr">
         <is>
           <t>今回は買わないもの</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="5" t="inlineStr">
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>品目</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>商品</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>価格（円）</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>外した理由</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
-    </row>
-    <row r="29" ht="34" customHeight="1">
-      <c r="A29" s="16" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr"/>
+      <c r="F26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27" ht="34" customHeight="1">
+      <c r="A27" s="18" t="inlineStr">
         <is>
           <t>ジンバル</t>
         </is>
       </c>
-      <c r="B29" s="17" t="inlineStr">
+      <c r="B27" s="19" t="inlineStr">
         <is>
           <t>Zhiyun Crane M3</t>
         </is>
       </c>
-      <c r="C29" s="18" t="n">
+      <c r="C27" s="20" t="n">
         <v>20710</v>
       </c>
-      <c r="D29" s="17" t="inlineStr">
+      <c r="D27" s="19" t="inlineStr">
         <is>
           <t>④の街歩きと⑥の工房を歩くカットの手ブレを抑える機材。三脚と手持ちでも撮影は成立するため、必要性を感じてからで良い</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="34" customHeight="1">
-      <c r="A30" s="16" t="inlineStr">
+    <row r="28" ht="34" customHeight="1">
+      <c r="A28" s="18" t="inlineStr">
         <is>
           <t>予備バッテリー</t>
         </is>
       </c>
-      <c r="B30" s="17" t="inlineStr">
+      <c r="B28" s="19" t="inlineStr">
         <is>
           <t>NP-FW50 互換2個＋充電器セット</t>
         </is>
       </c>
-      <c r="C30" s="18" t="n">
+      <c r="C28" s="20" t="n">
         <v>3300</v>
       </c>
-      <c r="D30" s="17" t="inlineStr">
+      <c r="D28" s="19" t="inlineStr">
         <is>
           <t>1日で撮り切らず日を分ければ、本体付属の1個で回せる</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="19" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
         <is>
           <t>削減額</t>
         </is>
       </c>
-      <c r="C31" s="20">
-        <f>SUM(C29:C30)</f>
+      <c r="C29" s="22">
+        <f>SUM(C27:C28)</f>
         <v/>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="23" t="inlineStr">
+        <is>
+          <t>評価とサクラチェックについて</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>・カメラとレンズはソニー純正、音声はZOOMとRODEという実績あるメーカーの公式販売ページから選びました。</t>
+        </is>
+      </c>
+    </row>
     <row r="34">
-      <c r="A34" s="21" t="inlineStr">
-        <is>
-          <t>評価とサクラチェックについて</t>
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>・無名ブランドの安価な製品はレビューが操作されている可能性があるため、音声機材からは外しています</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>・カメラとレンズはソニー純正、音声はZOOMとRODEという実績あるメーカーの公式販売ページから選びました。</t>
+          <t xml:space="preserve">　（前回案のワイヤレスピンマイク13,999円もこれに該当するため差し替えました）。</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>・無名ブランドの安価な製品はレビューが操作されている可能性があるため、音声機材からは外しています</t>
+          <t>・この資料の作成環境からは sakura-checker.jp に直接アクセスできず、自動でサクラ度を判定できませんでした。</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">　（前回案のワイヤレスピンマイク13,999円もこれに該当するため差し替えました）。</t>
+          <t xml:space="preserve">　メーカー公式ページであること、レビュー件数と評価を根拠にしています。</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>・この資料の作成環境からは sakura-checker.jp に直接アクセスできず、自動でサクラ度を判定できませんでした。</t>
+          <t>・発注前に、商品ページのURLをサクラチェッカーに貼り付けてご自身でもご確認ください（数秒で判定が出ます）。</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　メーカー公式ページであること、レビュー件数と評価を根拠にしています。</t>
-        </is>
-      </c>
+      <c r="A39" s="1" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>・発注前に、商品ページのURLをサクラチェッカーに貼り付けてご自身でもご確認ください（数秒で判定が出ます）。</t>
+      <c r="A40" s="23" t="inlineStr">
+        <is>
+          <t>商品ページのリンクについて</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="inlineStr"/>
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>・全リンクを商品名で検索し直し、amazon.co.jpに実在するページかを1件ずつ照合しました（結果は右端の列）。</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>将来の余地：カメラ本体をSONY ZV-E10 II（約140,000円）に替えると合計は約219,000円。暗い工房での画質に差が出ます。</t>
+          <t>・ガンマイクのリンクが米国Amazon由来のASINになっていたため、国内ページに差し替えました。</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>撮影するカットの一覧は別ファイル「02_場面別ショットリスト.xlsx」にあります。</t>
+          <t>・音声レコーダーは検索リンクだったため、商品ページに差し替えました。</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>・この環境からはamazon.co.jpを直接開けないため、検索結果のタイトルとASINでの照合です。購入前に商品名をご確認ください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>注意：マクロレンズはソニーEマウント専用です。お使いのカメラが別マウントの場合は、同じ焦点距離帯のマクロレンズに置き換えてください（金額はおおむね2〜4万円）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>撮影するカットの一覧は別ファイル「02_場面別ショットリスト.xlsx」にあります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
         <is>
           <t>価格は2026年9月時点の実売価格です。</t>
         </is>
@@ -1163,15 +1207,14 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pdf/01_撮影機材と費用.xlsx
+++ b/pdf/01_撮影機材と費用.xlsx
@@ -565,7 +565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -705,7 +705,7 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>国内カメラ用品の老舗メーカー・入門定番</t>
+          <t>国内カメラ用品の老舗メーカー・入門定番。価格は約3,000円だが、6,018円の掲載もあり要確認</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>ZOOM公式・評価4.5／5（32件）・32bitフロートで音割れしない</t>
+          <t>ZOOM公式。評価4.53／5・32件（Yahoo!ショッピング掲載値。Amazonの評価ではありません）。32bitフロートで音割れしない</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>レビュー件数の多い定番品</t>
+          <t>レビュー件数の多い定番品。今回の再確認では実売価格を確定できず、1,099円は前回調査時の値</t>
         </is>
       </c>
       <c r="F14" s="9" t="inlineStr">
@@ -1143,62 +1143,76 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="inlineStr"/>
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>・価格の確度：マクロレンズ・レコーダー・ガンマイク・照明・黒スチレンボードは今回の再確認で実売価格を確認済み。</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="23" t="inlineStr">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　三脚とレフ板は確定できず（三脚は約3,000円と6,018円の両方の掲載あり）、アクリル板とSDカードは概算です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="23" t="inlineStr">
         <is>
           <t>商品ページのリンクについて</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>・全リンクを商品名で検索し直し、amazon.co.jpに実在するページかを1件ずつ照合しました（結果は右端の列）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr">
-        <is>
-          <t>・ガンマイクのリンクが米国Amazon由来のASINになっていたため、国内ページに差し替えました。</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>・音声レコーダーは検索リンクだったため、商品ページに差し替えました。</t>
+          <t>・全リンクを商品名で検索し直し、amazon.co.jpに実在するページかを1件ずつ照合しました（結果は右端の列）。</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>・この環境からはamazon.co.jpを直接開けないため、検索結果のタイトルとASINでの照合です。購入前に商品名をご確認ください。</t>
+          <t>・ガンマイクのリンクが米国Amazon由来のASINになっていたため、国内ページに差し替えました。</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="inlineStr"/>
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>・音声レコーダーは検索リンクだったため、商品ページに差し替えました。</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>注意：マクロレンズはソニーEマウント専用です。お使いのカメラが別マウントの場合は、同じ焦点距離帯のマクロレンズに置き換えてください（金額はおおむね2〜4万円）。</t>
+          <t>・この環境からはamazon.co.jpを直接開けないため、検索結果のタイトルとASINでの照合です。購入前に商品名をご確認ください。</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="inlineStr">
-        <is>
-          <t>撮影するカットの一覧は別ファイル「02_場面別ショットリスト.xlsx」にあります。</t>
-        </is>
-      </c>
+      <c r="A47" s="1" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>注意：マクロレンズはソニーEマウント専用です。お使いのカメラが別マウントの場合は、同じ焦点距離帯のマクロレンズに置き換えてください（金額はおおむね2〜4万円）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>撮影するカットの一覧は別ファイル「02_場面別ショットリスト.xlsx」にあります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
         <is>
           <t>価格は2026年9月時点の実売価格です。</t>
         </is>
